--- a/buses_1.xlsx
+++ b/buses_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\EdioD\PycharmProjects\variacao-tensao-frp\13Bus\23742222\pyomo_data\model_reg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEAC724-D50C-40BB-A0BC-03C0755BB981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD349C8-8EA7-4878-8D09-46DDFFB69C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36720" yWindow="3885" windowWidth="13605" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2181,7 +2181,7 @@
         <v>0.48</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2210,7 +2210,7 @@
         <v>0.48</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>100</v>
@@ -2236,7 +2236,7 @@
         <v>0.48</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -2262,7 +2262,7 @@
         <v>0.48</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -2288,7 +2288,7 @@
         <v>0.48</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -2314,7 +2314,7 @@
         <v>0.48</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -2340,7 +2340,7 @@
         <v>0.48</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -2366,7 +2366,7 @@
         <v>0.48</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -2392,7 +2392,7 @@
         <v>0.48</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -2418,7 +2418,7 @@
         <v>0.48</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -2444,7 +2444,7 @@
         <v>0.48</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -2470,7 +2470,7 @@
         <v>0.48</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -2496,7 +2496,7 @@
         <v>0.48</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -2522,7 +2522,7 @@
         <v>0.48</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2548,7 +2548,7 @@
         <v>0.48</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -2574,7 +2574,7 @@
         <v>0.48</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>100</v>
@@ -2600,7 +2600,7 @@
         <v>0.48</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -2626,7 +2626,7 @@
         <v>0.48</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -2652,7 +2652,7 @@
         <v>0.48</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -2678,7 +2678,7 @@
         <v>0.48</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -2704,7 +2704,7 @@
         <v>0.48</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -2730,7 +2730,7 @@
         <v>0.48</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -2756,7 +2756,7 @@
         <v>0.48</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -2782,7 +2782,7 @@
         <v>0.48</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -2808,7 +2808,7 @@
         <v>0.48</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G26">
         <v>100</v>
@@ -2834,7 +2834,7 @@
         <v>0.48</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G27">
         <v>0</v>

--- a/buses_1.xlsx
+++ b/buses_1.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\EdioD\PycharmProjects\variacao-tensao-frp\13Bus\23742222\pyomo_data\model_reg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD349C8-8EA7-4878-8D09-46DDFFB69C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E273D01B-8F65-450E-B454-187D4AE2DF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="0" windowWidth="15375" windowHeight="7785" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="MT" sheetId="2" r:id="rId2"/>
-    <sheet name="BT" sheetId="3" r:id="rId3"/>
-    <sheet name="PV" sheetId="4" r:id="rId4"/>
+    <sheet name="Load_MT" sheetId="5" r:id="rId3"/>
+    <sheet name="BT" sheetId="3" r:id="rId4"/>
+    <sheet name="PV" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="138">
   <si>
     <t>N</t>
   </si>
@@ -438,6 +439,18 @@
   </si>
   <si>
     <t>q_pv_3</t>
+  </si>
+  <si>
+    <t>Conn</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>Wye</t>
   </si>
 </sst>
 </file>
@@ -510,12 +523,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2131,6 +2147,384 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38D994B-D0BD-40F0-89B6-F3D42977F0AD}">
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>671</v>
+      </c>
+      <c r="B2">
+        <v>4.16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2">
+        <v>1155</v>
+      </c>
+      <c r="E2">
+        <v>660</v>
+      </c>
+      <c r="F2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>634</v>
+      </c>
+      <c r="B3">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>160</v>
+      </c>
+      <c r="E3">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>634</v>
+      </c>
+      <c r="B4">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>634</v>
+      </c>
+      <c r="B5">
+        <v>0.27700000000000002</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="E5">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>645</v>
+      </c>
+      <c r="B6">
+        <v>2.4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>170</v>
+      </c>
+      <c r="E6">
+        <v>125</v>
+      </c>
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>646</v>
+      </c>
+      <c r="B7">
+        <v>4.16</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>230</v>
+      </c>
+      <c r="E7">
+        <v>132</v>
+      </c>
+      <c r="F7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>692</v>
+      </c>
+      <c r="B8">
+        <v>4.16</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>170</v>
+      </c>
+      <c r="E8">
+        <v>151</v>
+      </c>
+      <c r="F8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>675</v>
+      </c>
+      <c r="B9">
+        <v>2.4</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>485</v>
+      </c>
+      <c r="E9">
+        <v>190</v>
+      </c>
+      <c r="F9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>675</v>
+      </c>
+      <c r="B10">
+        <v>2.4</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>68</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>675</v>
+      </c>
+      <c r="B11">
+        <v>2.4</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>290</v>
+      </c>
+      <c r="E11">
+        <v>212</v>
+      </c>
+      <c r="F11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>611</v>
+      </c>
+      <c r="B12">
+        <v>2.4</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>170</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>652</v>
+      </c>
+      <c r="B13">
+        <v>2.4</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>128</v>
+      </c>
+      <c r="E13">
+        <v>86</v>
+      </c>
+      <c r="F13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>670</v>
+      </c>
+      <c r="B14">
+        <v>2.4</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>670</v>
+      </c>
+      <c r="B15">
+        <v>2.4</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>66</v>
+      </c>
+      <c r="E15">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>670</v>
+      </c>
+      <c r="B16">
+        <v>2.4</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>117</v>
+      </c>
+      <c r="E16">
+        <v>68</v>
+      </c>
+      <c r="F16" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F6DECE-9BDD-4A17-B474-5E7879AE55FA}">
   <dimension ref="A1:J56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3632,7 +4026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEAADF9-A235-4847-B98B-1C70DC88E2B7}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/buses_1.xlsx
+++ b/buses_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E273D01B-8F65-450E-B454-187D4AE2DF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FD6932-A868-48EB-9BC1-99C0ECFEAE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="0" windowWidth="15375" windowHeight="7785" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="138">
   <si>
     <t>N</t>
   </si>
@@ -523,15 +523,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2148,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38D994B-D0BD-40F0-89B6-F3D42977F0AD}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2167,31 +2164,31 @@
       <c r="E1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="B2">
-        <v>4.16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
+        <v>2.4</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1155</v>
+        <v>170</v>
       </c>
       <c r="E2">
-        <v>660</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2199,65 +2196,65 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="B3">
-        <v>0.27700000000000002</v>
+        <v>4.16</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="E3">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>634</v>
+        <v>692</v>
       </c>
       <c r="B4">
-        <v>0.27700000000000002</v>
+        <v>4.16</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E4">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>634</v>
+        <v>675</v>
       </c>
       <c r="B5">
-        <v>0.27700000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>485</v>
       </c>
       <c r="E5">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
         <v>137</v>
@@ -2268,7 +2265,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>645</v>
+        <v>675</v>
       </c>
       <c r="B6">
         <v>2.4</v>
@@ -2277,10 +2274,10 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="E6">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
         <v>137</v>
@@ -2291,33 +2288,33 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>646</v>
+        <v>675</v>
       </c>
       <c r="B7">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="E7">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>692</v>
+        <v>611</v>
       </c>
       <c r="B8">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2326,10 +2323,10 @@
         <v>170</v>
       </c>
       <c r="E8">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -2337,7 +2334,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="B9">
         <v>2.4</v>
@@ -2346,33 +2343,33 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>485</v>
+        <v>128</v>
       </c>
       <c r="E9">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
         <v>137</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B10">
         <v>2.4</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>137</v>
@@ -2383,19 +2380,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B11">
         <v>2.4</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>290</v>
+        <v>66</v>
       </c>
       <c r="E11">
-        <v>212</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>137</v>
@@ -2406,7 +2403,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>611</v>
+        <v>670</v>
       </c>
       <c r="B12">
         <v>2.4</v>
@@ -2415,107 +2412,15 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="E12">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
         <v>137</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>652</v>
-      </c>
-      <c r="B13">
-        <v>2.4</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>128</v>
-      </c>
-      <c r="E13">
-        <v>86</v>
-      </c>
-      <c r="F13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>670</v>
-      </c>
-      <c r="B14">
-        <v>2.4</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>17</v>
-      </c>
-      <c r="E14">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>670</v>
-      </c>
-      <c r="B15">
-        <v>2.4</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>66</v>
-      </c>
-      <c r="E15">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>670</v>
-      </c>
-      <c r="B16">
-        <v>2.4</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>117</v>
-      </c>
-      <c r="E16">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>
